--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_once_tower_challenge/lang_once_tower_challenge__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_once_tower_challenge/lang_once_tower_challenge__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất 1</t>
+          <t>Rèn Luyện Thể Chất 1</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Thể lực là nền tảng của thám hiểm, hãy tận dụng các buổi tập luyện để thích nghi tốt hơn với môi trường dưới lòng đất.</t>
+          <t>Thể lực là nền tảng của việc thám hiểm, hãy tận dụng các buổi rèn luyện để thích nghi tốt hơn với cuộc sống dưới lòng đất.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất 1</t>
+          <t>Rèn Luyện Thể Chất 1</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất 2</t>
+          <t>Rèn Luyện Thể Chất 2</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Thể lực là nền tảng của thám hiểm, hãy tận dụng các buổi tập luyện để thích nghi tốt hơn với môi trường dưới lòng đất.</t>
+          <t>Thể lực là nền tảng của việc thám hiểm, hãy tận dụng các buổi rèn luyện để thích nghi tốt hơn với cuộc sống dưới lòng đất.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất 2</t>
+          <t>Rèn Luyện Thể Chất 2</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất 3</t>
+          <t>Rèn Luyện Thể Chất 3</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Thể lực là nền tảng của thám hiểm, hãy tận dụng các buổi tập luyện để thích nghi tốt hơn với môi trường dưới lòng đất.</t>
+          <t>Thể lực là nền tảng của việc thám hiểm, hãy tận dụng các buổi rèn luyện để thích nghi tốt hơn với cuộc sống dưới lòng đất.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất 3</t>
+          <t>Rèn Luyện Thể Chất 3</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất 4</t>
+          <t>Rèn Luyện Thể Chất 4</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Thể lực là nền tảng của thám hiểm, hãy tận dụng các buổi tập luyện để thích nghi tốt hơn với môi trường dưới lòng đất.</t>
+          <t>Thể lực là nền tảng của việc thám hiểm, hãy tận dụng các buổi rèn luyện để thích nghi tốt hơn với cuộc sống dưới lòng đất.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất 4</t>
+          <t>Rèn Luyện Thể Chất 4</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Trial Combat 1</t>
+          <t>Thử Thách Chiến Đấu 1</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Các trận chiến dưới lòng đất khác với trên mặt đất, tốt nhất cậu nên cẩn thận.</t>
+          <t>Những trận chiến diễn ra dưới lòng đất khác biệt so với trên mặt đất, tốt nhất bạn nên cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Trial Combat 1</t>
+          <t>Thử Thách Chiến Đấu 1</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Trial Combat 2</t>
+          <t>Thử Thách Chiến Đấu 2</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Các trận chiến dưới lòng đất khác với trên mặt đất, tốt nhất cậu nên cẩn thận.</t>
+          <t>Những trận chiến diễn ra dưới lòng đất khác biệt so với trên mặt đất, tốt nhất bạn nên cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Trial Combat 2</t>
+          <t>Thử Thách Chiến Đấu 2</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Các trận chiến dưới lòng đất khác với trên mặt đất, tốt nhất cậu nên cẩn thận.</t>
+          <t>Những trận chiến diễn ra dưới lòng đất khác biệt so với trên mặt đất, tốt nhất bạn nên cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Trial Combat 4</t>
+          <t>Thử Thách Chiến Đấu 4</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Các trận chiến dưới lòng đất khác với trên mặt đất, tốt nhất cậu nên cẩn thận.</t>
+          <t>Những trận chiến diễn ra dưới lòng đất khác biệt so với trên mặt đất, tốt nhất bạn nên cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Trial Combat 4</t>
+          <t>Thử Thách Chiến Đấu 4</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế 1</t>
+          <t>Mô phỏng Trực tiếp 1</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Mô phỏng thực tế có thể cải thiện khả năng thích ứng. Đây là cách tốt nhất để đạt được hiệu suất tối ưu trong chiến đấu.</t>
+          <t>Mô phỏng thực tế có thể nâng cao khả năng thích ứng. Đây là cách tốt nhất để tối ưu hóa hiệu suất chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế 1</t>
+          <t>Mô phỏng Trực tiếp 1</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế 2</t>
+          <t>Mô phỏng Trực tiếp 2</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Mô phỏng thực tế có thể cải thiện khả năng thích ứng. Đây là cách tốt nhất để đạt được hiệu suất tối ưu trong chiến đấu.</t>
+          <t>Mô phỏng thực tế có thể nâng cao khả năng thích ứng. Đây là cách tốt nhất để tối ưu hóa hiệu suất chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế 2</t>
+          <t>Mô phỏng Trực tiếp 2</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế 3</t>
+          <t>Mô phỏng Trực tiếp 3</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Mô phỏng thực tế có thể cải thiện khả năng thích ứng. Đây là cách tốt nhất để đạt được hiệu suất tối ưu trong chiến đấu.</t>
+          <t>Mô phỏng thực tế có thể nâng cao khả năng thích ứng. Đây là cách tốt nhất để tối ưu hóa hiệu suất chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế 3</t>
+          <t>Mô phỏng Trực tiếp 3</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế 4</t>
+          <t>Mô phỏng Trực tiếp 4</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Mô phỏng thực tế có thể cải thiện khả năng thích ứng. Đây là cách tốt nhất để đạt được hiệu suất tối ưu trong chiến đấu.</t>
+          <t>Mô phỏng thực tế có thể nâng cao khả năng thích ứng. Đây là cách tốt nhất để tối ưu hóa hiệu suất chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế 4</t>
+          <t>Mô phỏng Trực tiếp 4</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Mọi thứ đã chuẩn bị xong, giấy phép này là của cậu rồi!</t>
+          <t>Mọi thứ đã chuẩn bị xong, giấy phép đã nằm trong tầm tay rồi!</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Thao tác thất bại, xem lại chiến thuật và thử lại.</t>
+          <t>Thao tác thất bại, hãy cân nhắc lại chiến thuật và thử lại.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất</t>
+          <t>Huấn luyện Vật lý</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Huấn Luyện Thể Chất</t>
+          <t>Huấn luyện Vật lý</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Trial Combat</t>
+          <t>Thử Thách Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Trial Combat</t>
+          <t>Thử Thách Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế</t>
+          <t>Mô phỏng Trực tiếp</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Mô Phỏng Thực Tế</t>
+          <t>Mô phỏng Trực tiếp</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Concerto Overture</t>
+          <t>Khúc dạo đầu Concerto</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Tất cả thành viên nhận thêm Concerto Vibrancy.</t>
+          <t>Tất cả thành viên nhận thêm Nhịp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Nhận thêm Resonance Energy khi bất kỳ nhân vật nào kích hoạt Concerto Effect.</t>
+          <t>Nhận thêm Resonance Energy khi bất kỳ nhân vật nào kích hoạt Hiệu Ứng Concerto.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Resonance Pirouette</t>
+          <t>Vũ Điệu Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Mỗi khi sử dụng Resonance Liberation, toàn đội nhận tăng 20% DMG trong 12 giây.</t>
+          <t>Mỗi lần sử dụng Resonance Liberation, toàn đội nhận tăng 20% sát thương trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Feathering Ode</t>
+          <t>Khúc Ngâm Lông Vũ</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Sau khi Dodge hoàn hảo, nhận tăng 20% Crit. Rate, cộng dồn tối đa 3 lần, hiệu ứng kéo dài 8 giây, Dodge lặp lại sẽ làm mới thời gian.</t>
+          <t>Sau khi né tránh hoàn hảo, nhận tăng 20% Crit. Rate, có thể chồng chất tối đa 3 lần, hiệu ứng kéo dài 8 giây, né tránh liên tiếp sẽ làm mới thời gian hiệu lực.</t>
         </is>
       </c>
     </row>
